--- a/public/管理口径原因分析默认模版/南京项目部.xlsx
+++ b/public/管理口径原因分析默认模版/南京项目部.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12375" firstSheet="21" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="208">
   <si>
     <t>工作表目录</t>
   </si>
@@ -128,7 +128,7 @@
     <t>江苏淮安销售分公司配餐劳务项目</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年07月）</t>
+    <t>合计预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -222,6 +222,9 @@
     <t xml:space="preserve">                  3.外购动力</t>
   </si>
   <si>
+    <t>承租方日常经营用电</t>
+  </si>
+  <si>
     <t xml:space="preserve">                  4.商旅采购成本</t>
   </si>
   <si>
@@ -259,6 +262,9 @@
   </si>
   <si>
     <t xml:space="preserve">        （七）维修费</t>
+  </si>
+  <si>
+    <t>维修节约</t>
   </si>
   <si>
     <t xml:space="preserve">        （八）租赁费</t>
@@ -380,7 +386,7 @@
     <t>主要因所得税汇算清缴25年已预提及新增配餐增加利润</t>
   </si>
   <si>
-    <t>江苏销售分公司配餐业务预算执行分析（2026年07月）</t>
+    <t>江苏销售分公司配餐业务预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目据实结算，原东北销售南京分部分人员转移此用餐</t>
@@ -395,7 +401,7 @@
     <t>采购0.9万碗具器材</t>
   </si>
   <si>
-    <t>新上系统，去年5月人工没进系统</t>
+    <t>去年同期人工于9月入账</t>
   </si>
   <si>
     <t>预算为框架合同额度，人工为实际发生</t>
@@ -404,13 +410,13 @@
     <t>江苏销售去年7月单月有二季度结算，本年季度结算在6月，季度结算时会有实际结算与预估差异。</t>
   </si>
   <si>
-    <t>江苏非油销售公司劳务输出预算执行分析（2026年07月）</t>
+    <t>江苏非油销售公司劳务输出预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目合同2025年1月16日到期，用工2人1月人工已结清，自然终止无补偿金。</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_合并预算执行分析（2026年07月）</t>
+    <t>江苏南京销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>同期比较增加原因今年合同额增加。</t>
@@ -422,13 +428,13 @@
     <t>新上系统，去年5月人工没进系统，并新合同，增加一人</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_222200150520预算执行分析（2026年07月）</t>
+    <t>江苏南京销售分公司劳务输出_222200150520预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_SH3J25Z017预算执行分析（2026年07月）</t>
+    <t>江苏南京销售分公司劳务输出_SH3J25Z017预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江南京分公司配餐业务预算执行分析（2026年07月）</t>
+    <t>东北销售浙江南京分公司配餐业务预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新上系统，去年5月收入未进账</t>
@@ -443,7 +449,7 @@
     <t>根据收入比例计提税费</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_合并预算执行分析（2026年07月）</t>
+    <t>江苏南京中石油联安石化办公物业_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新上系统，去年5月收入同比未入账</t>
@@ -467,13 +473,13 @@
     <t>4人未交社保减少成本利润增加</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_222200150531预算执行分析（2026年07月）</t>
+    <t>江苏南京中石油联安石化办公物业_222200150531预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_SH3626Z003预算执行分析（2026年07月）</t>
+    <t>江苏南京中石油联安石化办公物业_SH3626Z003预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_合并预算执行分析（2026年07月）</t>
+    <t>江苏镇江销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新上系统，去年5月收入未入账</t>
@@ -485,13 +491,13 @@
     <t>人工加班费成本增加利润下降</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_222200150532预算执行分析（2026年07月）</t>
+    <t>江苏镇江销售分公司劳务输出_222200150532预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_SH3J26Z001预算执行分析（2026年07月）</t>
+    <t>江苏镇江销售分公司劳务输出_SH3J26Z001预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>秣陵路99号综合楼酒店整租项目预算执行分析（2026年07月）</t>
+    <t>秣陵路99号综合楼酒店整租项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <r>
@@ -539,7 +545,7 @@
     <t>蓝海加油卡下半年由南通项目部承担</t>
   </si>
   <si>
-    <t>公共区域水电1-5月共减少</t>
+    <t>公共区域水电1-9月减少</t>
   </si>
   <si>
     <t>运输费减少</t>
@@ -558,6 +564,9 @@
   </si>
   <si>
     <t>劳务外包员工部分人工为配餐项目分摊</t>
+  </si>
+  <si>
+    <t>维修费同比节约</t>
   </si>
   <si>
     <t>维修电脑维修费同比节约</t>
@@ -593,19 +602,16 @@
     <t>主要因素为所得税汇算清缴已在25年预提</t>
   </si>
   <si>
-    <t>黄鹂新村8栋酒店整租项目预算执行分析（2026年07月）</t>
+    <t>黄鹂新村8栋酒店整租项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>减免7月收入</t>
+    <t>减免7月、8月收入</t>
   </si>
   <si>
-    <t>减免7月收入相关税费减少</t>
+    <t>减免7月、8月收入相关税费减少</t>
   </si>
   <si>
-    <t>主要原因减免7月收入</t>
-  </si>
-  <si>
-    <t>黄鹂新村、金斯利、南湖住宅其他资产租赁项目预算执行分析（2026年07月）</t>
+    <t>黄鹂新村、金斯利、南湖住宅其他资产租赁项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t xml:space="preserve">同比租金协议下降 </t>
@@ -617,19 +623,19 @@
     <t>同比租金协议下降，影响利润</t>
   </si>
   <si>
-    <t>南京项目部项目销售预算执行分析（2026年07月）</t>
+    <t>南京项目部项目销售预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>粽子销售客源流失</t>
   </si>
   <si>
-    <t>南京酒店能源转售项目预算执行分析（2026年07月）</t>
+    <t>南京酒店能源转售项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>非盈利项目</t>
   </si>
   <si>
-    <t>中国移动南京分公司基站预算执行分析（2026年07月）</t>
+    <t>中国移动南京分公司基站预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>移动租金递增</t>
@@ -642,7 +648,7 @@
 </t>
   </si>
   <si>
-    <t>中国铁塔南京市分公司基站预算执行分析（2026年07月）</t>
+    <t>中国铁塔南京市分公司基站预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>同比租金下降</t>
@@ -658,7 +664,7 @@
 </t>
   </si>
   <si>
-    <t>合肥昆仑燃气配餐项目预算执行分析（2026年07月）</t>
+    <t>合肥昆仑燃气配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>食材据实结算</t>
@@ -670,7 +676,7 @@
     <t>新增零星用餐业务收入新增利润</t>
   </si>
   <si>
-    <t>天然气安徽分配餐项目预算执行分析（2026年07月）</t>
+    <t>天然气安徽分配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新能源部门调到其他地方</t>
@@ -682,7 +688,7 @@
     <t>聘用3名退休人员，控人工成本</t>
   </si>
   <si>
-    <t>中石油昆仑合燃压缩气配餐项目预算执行分析（2026年07月）</t>
+    <t>中石油昆仑合燃压缩气配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>去年新增项目</t>
@@ -691,7 +697,7 @@
     <t>收入根据食材有所变动</t>
   </si>
   <si>
-    <t>东北销售南京分计量服务项目预算执行分析（2026年07月）</t>
+    <t>东北销售南京分计量服务项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>原合同预算按3月终止，因续签1年延长了存续期，收入偏差较大</t>
@@ -700,13 +706,13 @@
     <t>原合同预算按3月终止，因续签1年延长了存续期，人工偏差较大</t>
   </si>
   <si>
-    <t>去年同期进错WBS造成利润暂时性增加</t>
+    <t>多结算收入已转合同负债，同期未收入成本配比，造成利润虚增</t>
   </si>
   <si>
     <t>原合同预算按3月终止，净利润指标2.7万元，因续签1年延长了存续期，利润偏差较大</t>
   </si>
   <si>
-    <t>江苏淮安销售分公司配餐劳务项目预算执行分析（2026年07月）</t>
+    <t>江苏淮安销售分公司配餐劳务项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新增项目</t>
@@ -1217,7 +1223,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1287,11 +1293,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -1309,7 +1315,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -1447,7 +1453,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1465,7 +1471,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -1483,7 +1489,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1501,7 +1507,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -1509,7 +1515,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -1521,7 +1527,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1539,7 +1545,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -1547,7 +1553,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -1559,7 +1565,7 @@
     </row>
     <row r="18" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1567,11 +1573,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -1581,7 +1587,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1599,7 +1605,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1617,7 +1623,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1635,7 +1641,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1653,7 +1659,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1671,7 +1677,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1689,7 +1695,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -1707,7 +1713,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1725,7 +1731,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1743,7 +1749,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1761,7 +1767,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1779,7 +1785,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1797,7 +1803,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1815,7 +1821,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1833,7 +1839,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1851,7 +1857,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1869,7 +1875,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1887,7 +1893,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -1905,7 +1911,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -1923,7 +1929,7 @@
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1931,11 +1937,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -1945,7 +1951,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1963,7 +1969,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2000,7 +2006,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2224,7 +2230,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -2242,7 +2248,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -2260,7 +2266,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -2278,7 +2284,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -2296,7 +2302,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -2314,7 +2320,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2332,7 +2338,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2350,7 +2356,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2368,7 +2374,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2386,7 +2392,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2404,7 +2410,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2422,7 +2428,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2440,7 +2446,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2458,7 +2464,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2476,7 +2482,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2494,7 +2500,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2512,7 +2518,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2530,7 +2536,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2548,7 +2554,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2566,7 +2572,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2584,7 +2590,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2602,7 +2608,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2620,7 +2626,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2638,7 +2644,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2656,7 +2662,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2674,7 +2680,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2692,7 +2698,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2710,7 +2716,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2728,7 +2734,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2765,7 +2771,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2989,7 +2995,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -3007,7 +3013,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -3025,7 +3031,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3043,7 +3049,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3061,7 +3067,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3079,7 +3085,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3097,7 +3103,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3115,7 +3121,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3133,7 +3139,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3151,7 +3157,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3169,7 +3175,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3187,7 +3193,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3205,7 +3211,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3223,7 +3229,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3241,7 +3247,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3259,7 +3265,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3277,7 +3283,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3295,7 +3301,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3313,7 +3319,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3331,7 +3337,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3349,7 +3355,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3367,7 +3373,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3385,7 +3391,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3403,7 +3409,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3421,7 +3427,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3439,7 +3445,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3457,7 +3463,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -3475,7 +3481,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3493,7 +3499,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3530,7 +3536,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3600,11 +3606,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -3758,7 +3764,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -3776,7 +3782,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -3794,7 +3800,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3812,7 +3818,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -3830,7 +3836,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -3848,7 +3854,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3866,7 +3872,7 @@
     </row>
     <row r="18" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -3874,11 +3880,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -3888,7 +3894,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3906,7 +3912,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3924,7 +3930,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3942,7 +3948,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3960,7 +3966,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3978,7 +3984,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3996,7 +4002,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4014,7 +4020,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4032,7 +4038,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4050,7 +4056,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4068,7 +4074,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4086,7 +4092,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4104,7 +4110,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4122,7 +4128,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4140,7 +4146,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4158,7 +4164,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4176,7 +4182,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4194,7 +4200,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4212,7 +4218,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4230,7 +4236,7 @@
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4238,7 +4244,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -4250,7 +4256,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4268,7 +4274,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4305,7 +4311,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4529,7 +4535,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -4547,7 +4553,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -4565,7 +4571,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -4583,7 +4589,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -4601,7 +4607,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -4619,7 +4625,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -4637,7 +4643,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -4655,7 +4661,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4673,7 +4679,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4691,7 +4697,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4709,7 +4715,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4727,7 +4733,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4745,7 +4751,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -4763,7 +4769,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4781,7 +4787,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4799,7 +4805,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4817,7 +4823,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4835,7 +4841,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4853,7 +4859,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4871,7 +4877,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4889,7 +4895,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4907,7 +4913,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4925,7 +4931,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4943,7 +4949,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4961,7 +4967,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4979,7 +4985,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4997,7 +5003,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -5015,7 +5021,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -5033,7 +5039,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -5070,7 +5076,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5294,7 +5300,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -5312,7 +5318,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -5330,7 +5336,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -5348,7 +5354,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -5366,7 +5372,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -5384,7 +5390,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -5402,7 +5408,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -5420,7 +5426,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -5438,7 +5444,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -5456,7 +5462,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -5474,7 +5480,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -5492,7 +5498,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -5510,7 +5516,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -5528,7 +5534,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -5546,7 +5552,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5564,7 +5570,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -5582,7 +5588,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -5600,7 +5606,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -5618,7 +5624,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -5636,7 +5642,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -5654,7 +5660,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -5672,7 +5678,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -5690,7 +5696,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -5708,7 +5714,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -5726,7 +5732,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -5744,7 +5750,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -5762,7 +5768,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -5780,7 +5786,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -5798,7 +5804,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -5835,7 +5841,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5905,7 +5911,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -5943,11 +5949,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -6037,11 +6043,11 @@
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H10" s="11"/>
       <c r="I10" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -6059,7 +6065,7 @@
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -6071,7 +6077,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -6089,7 +6095,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -6107,7 +6113,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -6115,7 +6121,7 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="12"/>
@@ -6127,7 +6133,7 @@
     </row>
     <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -6135,11 +6141,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -6149,7 +6155,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -6167,7 +6173,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -6175,7 +6181,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -6187,7 +6193,7 @@
     </row>
     <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -6195,11 +6201,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -6209,7 +6215,7 @@
     </row>
     <row r="19" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6217,11 +6223,11 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
@@ -6231,7 +6237,7 @@
     </row>
     <row r="20" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6239,11 +6245,11 @@
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -6253,7 +6259,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6271,7 +6277,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6289,7 +6295,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6297,11 +6303,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -6311,7 +6317,7 @@
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6319,11 +6325,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -6333,7 +6339,7 @@
     </row>
     <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6341,7 +6347,7 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12"/>
@@ -6353,7 +6359,7 @@
     </row>
     <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -6361,11 +6367,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -6375,7 +6381,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6393,7 +6399,7 @@
     </row>
     <row r="28" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -6401,11 +6407,11 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -6415,7 +6421,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -6433,7 +6439,7 @@
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -6441,11 +6447,11 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -6455,7 +6461,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -6473,7 +6479,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6491,7 +6497,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -6509,7 +6515,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -6527,7 +6533,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -6545,7 +6551,7 @@
     </row>
     <row r="36" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -6553,7 +6559,7 @@
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
       <c r="G36" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H36" s="11"/>
       <c r="I36" s="12"/>
@@ -6565,7 +6571,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -6583,7 +6589,7 @@
     </row>
     <row r="38" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6591,11 +6597,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -6605,7 +6611,7 @@
     </row>
     <row r="39" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -6613,7 +6619,7 @@
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="12"/>
@@ -6625,7 +6631,7 @@
     </row>
     <row r="40" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -6633,7 +6639,7 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12"/>
@@ -6664,7 +6670,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -6734,11 +6740,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -6892,7 +6898,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -6910,7 +6916,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -6928,7 +6934,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -6946,7 +6952,7 @@
     </row>
     <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -6954,7 +6960,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -6966,7 +6972,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -6984,7 +6990,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7002,7 +7008,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7020,7 +7026,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7038,7 +7044,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7056,7 +7062,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7074,7 +7080,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7092,7 +7098,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7110,7 +7116,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7128,7 +7134,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7146,7 +7152,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7164,7 +7170,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7182,7 +7188,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7200,7 +7206,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7218,7 +7224,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7236,7 +7242,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7254,7 +7260,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7272,7 +7278,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7290,7 +7296,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7308,7 +7314,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7326,7 +7332,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7344,7 +7350,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -7362,7 +7368,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -7370,7 +7376,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -7382,7 +7388,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -7400,14 +7406,16 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+      <c r="G40" s="12" t="s">
+        <v>170</v>
+      </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12"/>
       <c r="J40" s="11"/>
@@ -7437,7 +7445,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7507,11 +7515,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -7665,7 +7673,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -7683,7 +7691,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -7701,7 +7709,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -7719,7 +7727,7 @@
     </row>
     <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -7727,11 +7735,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -7741,7 +7749,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -7759,7 +7767,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -7777,7 +7785,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -7795,7 +7803,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7813,7 +7821,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7831,7 +7839,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7849,7 +7857,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7867,7 +7875,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7885,7 +7893,7 @@
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7893,11 +7901,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -7907,7 +7915,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7925,7 +7933,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7943,7 +7951,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7961,7 +7969,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7979,7 +7987,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7997,7 +8005,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -8015,7 +8023,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -8033,7 +8041,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -8051,7 +8059,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -8069,7 +8077,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -8087,7 +8095,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -8105,7 +8113,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -8123,7 +8131,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -8141,7 +8149,7 @@
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -8149,11 +8157,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -8163,7 +8171,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8181,7 +8189,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -8218,7 +8226,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8290,7 +8298,7 @@
       <c r="G3" s="12"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -8444,7 +8452,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -8462,7 +8470,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -8480,7 +8488,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -8498,7 +8506,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -8516,7 +8524,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -8534,7 +8542,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -8552,7 +8560,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -8570,7 +8578,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -8588,7 +8596,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -8606,7 +8614,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -8624,7 +8632,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -8642,7 +8650,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -8660,7 +8668,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -8678,7 +8686,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -8696,7 +8704,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -8714,7 +8722,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -8732,7 +8740,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -8750,7 +8758,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -8768,7 +8776,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -8786,7 +8794,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -8804,7 +8812,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -8822,7 +8830,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -8840,7 +8848,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -8858,7 +8866,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -8876,7 +8884,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -8894,7 +8902,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -8912,7 +8920,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -8930,7 +8938,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8948,7 +8956,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -9272,7 +9280,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -9342,7 +9350,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -9498,7 +9506,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -9516,7 +9524,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -9534,7 +9542,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -9552,7 +9560,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -9570,7 +9578,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -9588,7 +9596,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -9606,7 +9614,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -9624,7 +9632,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -9642,7 +9650,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -9660,7 +9668,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -9678,7 +9686,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -9696,7 +9704,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -9714,7 +9722,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -9732,7 +9740,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -9750,7 +9758,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -9768,7 +9776,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -9786,7 +9794,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -9804,7 +9812,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -9822,7 +9830,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -9840,7 +9848,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -9858,7 +9866,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -9876,7 +9884,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -9894,7 +9902,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -9912,7 +9920,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -9930,7 +9938,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -9948,7 +9956,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -9966,7 +9974,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -9984,7 +9992,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -10002,7 +10010,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -10039,7 +10047,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10109,7 +10117,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -10265,7 +10273,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -10283,7 +10291,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -10301,7 +10309,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -10319,7 +10327,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -10337,7 +10345,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -10355,7 +10363,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -10373,7 +10381,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -10391,7 +10399,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -10409,7 +10417,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -10427,7 +10435,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -10445,7 +10453,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -10463,7 +10471,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -10481,7 +10489,7 @@
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -10489,7 +10497,7 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12"/>
@@ -10501,7 +10509,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -10519,7 +10527,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -10537,7 +10545,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -10555,7 +10563,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -10573,7 +10581,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -10591,7 +10599,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -10609,7 +10617,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -10627,7 +10635,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -10645,7 +10653,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10663,7 +10671,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -10681,7 +10689,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -10699,7 +10707,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -10717,7 +10725,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -10735,7 +10743,7 @@
     </row>
     <row r="38" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -10743,7 +10751,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -10755,7 +10763,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -10773,7 +10781,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -10810,7 +10818,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10880,11 +10888,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -11038,7 +11046,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -11056,7 +11064,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -11074,7 +11082,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -11092,7 +11100,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -11100,7 +11108,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -11112,7 +11120,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -11130,7 +11138,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -11148,7 +11156,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -11166,7 +11174,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -11184,7 +11192,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -11202,7 +11210,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -11220,7 +11228,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -11238,7 +11246,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -11256,7 +11264,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -11274,7 +11282,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -11292,7 +11300,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -11310,7 +11318,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -11328,7 +11336,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -11346,7 +11354,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -11364,7 +11372,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -11382,7 +11390,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -11400,7 +11408,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -11418,7 +11426,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -11436,7 +11444,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -11454,7 +11462,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -11472,7 +11480,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -11490,7 +11498,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -11508,7 +11516,7 @@
     </row>
     <row r="38" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -11516,7 +11524,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -11528,7 +11536,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -11546,7 +11554,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -11583,7 +11591,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11671,11 +11679,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -11693,11 +11701,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -11715,11 +11723,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -11819,7 +11827,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -11837,7 +11845,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -11855,7 +11863,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -11873,7 +11881,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -11891,7 +11899,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -11909,7 +11917,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -11927,7 +11935,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -11935,11 +11943,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -11949,7 +11957,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -11967,7 +11975,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -11985,7 +11993,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -12003,7 +12011,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -12021,7 +12029,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -12039,7 +12047,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -12057,7 +12065,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -12075,7 +12083,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -12093,7 +12101,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -12111,7 +12119,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -12129,7 +12137,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -12147,7 +12155,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -12165,7 +12173,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -12183,7 +12191,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -12201,7 +12209,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -12219,7 +12227,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -12237,7 +12245,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -12255,7 +12263,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -12273,7 +12281,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -12291,7 +12299,7 @@
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -12299,7 +12307,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -12311,7 +12319,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -12329,7 +12337,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -12366,7 +12374,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -12454,11 +12462,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -12476,11 +12484,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -12498,11 +12506,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -12602,7 +12610,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -12620,7 +12628,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -12638,7 +12646,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -12656,7 +12664,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -12674,7 +12682,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -12692,7 +12700,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -12710,7 +12718,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -12718,11 +12726,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -12732,7 +12740,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -12750,7 +12758,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -12768,7 +12776,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -12786,7 +12794,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -12804,7 +12812,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -12822,7 +12830,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -12840,7 +12848,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -12858,7 +12866,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -12876,7 +12884,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -12894,7 +12902,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -12912,7 +12920,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -12930,7 +12938,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -12948,7 +12956,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -12966,7 +12974,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -12984,7 +12992,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -13002,7 +13010,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -13020,7 +13028,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -13038,7 +13046,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -13056,7 +13064,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -13074,7 +13082,7 @@
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -13082,7 +13090,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -13094,7 +13102,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -13112,7 +13120,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -13149,7 +13157,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -13219,11 +13227,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -13241,11 +13249,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -13263,11 +13271,11 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -13285,11 +13293,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -13389,7 +13397,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -13407,7 +13415,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -13425,7 +13433,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -13443,7 +13451,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -13461,7 +13469,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -13479,7 +13487,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -13497,7 +13505,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -13515,7 +13523,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -13533,7 +13541,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -13551,7 +13559,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -13569,7 +13577,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -13587,7 +13595,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -13605,7 +13613,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -13623,7 +13631,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -13641,7 +13649,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -13659,7 +13667,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -13677,7 +13685,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -13695,7 +13703,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -13713,7 +13721,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -13731,7 +13739,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -13749,7 +13757,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -13767,7 +13775,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -13785,7 +13793,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -13803,7 +13811,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -13821,7 +13829,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -13839,7 +13847,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -13857,7 +13865,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -13865,7 +13873,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -13877,7 +13885,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -13895,7 +13903,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -13932,7 +13940,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -14002,11 +14010,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -14160,7 +14168,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -14178,7 +14186,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -14196,7 +14204,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -14214,7 +14222,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -14232,7 +14240,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -14250,7 +14258,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -14268,7 +14276,7 @@
     </row>
     <row r="18" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -14276,11 +14284,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -14290,7 +14298,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -14308,7 +14316,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -14326,7 +14334,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -14344,7 +14352,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -14362,7 +14370,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -14380,7 +14388,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -14398,7 +14406,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -14416,7 +14424,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -14434,7 +14442,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -14452,7 +14460,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -14470,7 +14478,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -14488,7 +14496,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -14506,7 +14514,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -14524,7 +14532,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -14542,7 +14550,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -14560,7 +14568,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -14578,7 +14586,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -14596,7 +14604,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -14614,7 +14622,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -14632,7 +14640,7 @@
     </row>
     <row r="38" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -14640,11 +14648,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -14654,7 +14662,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -14672,7 +14680,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -14709,7 +14717,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -14779,11 +14787,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -14937,7 +14945,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -14955,7 +14963,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -14973,7 +14981,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -14991,7 +14999,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -15009,7 +15017,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -15027,7 +15035,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -15045,7 +15053,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -15053,7 +15061,7 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
@@ -15065,7 +15073,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -15083,7 +15091,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -15101,7 +15109,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -15119,7 +15127,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -15137,7 +15145,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -15155,7 +15163,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -15173,7 +15181,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -15191,7 +15199,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -15209,7 +15217,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -15227,7 +15235,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -15245,7 +15253,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -15263,7 +15271,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -15281,7 +15289,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -15299,7 +15307,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -15317,7 +15325,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -15335,7 +15343,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -15353,7 +15361,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -15371,7 +15379,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -15389,7 +15397,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -15407,7 +15415,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -15425,7 +15433,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -15443,7 +15451,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -15715,7 +15723,9 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="12" t="s">
+        <v>59</v>
+      </c>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
       <c r="J11" s="11"/>
@@ -15726,7 +15736,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -15744,7 +15754,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -15762,7 +15772,7 @@
     </row>
     <row r="14" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -15770,11 +15780,11 @@
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
       <c r="G14" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -15784,7 +15794,7 @@
     </row>
     <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -15792,11 +15802,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -15806,7 +15816,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -15824,7 +15834,7 @@
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -15832,11 +15842,11 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -15846,7 +15856,7 @@
     </row>
     <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -15854,11 +15864,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -15868,14 +15878,16 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
+      <c r="G19" s="12" t="s">
+        <v>73</v>
+      </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12"/>
       <c r="J19" s="11"/>
@@ -15886,7 +15898,7 @@
     </row>
     <row r="20" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -15894,11 +15906,11 @@
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -15908,7 +15920,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -15926,7 +15938,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -15944,7 +15956,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -15952,11 +15964,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -15966,7 +15978,7 @@
     </row>
     <row r="24" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -15974,7 +15986,7 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12"/>
@@ -15986,7 +15998,7 @@
     </row>
     <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -15994,11 +16006,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -16008,7 +16020,7 @@
     </row>
     <row r="26" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -16016,11 +16028,11 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -16030,7 +16042,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -16048,7 +16060,7 @@
     </row>
     <row r="28" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -16056,11 +16068,11 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -16070,7 +16082,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -16088,7 +16100,7 @@
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -16096,11 +16108,11 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -16110,7 +16122,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -16128,7 +16140,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -16146,7 +16158,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -16164,7 +16176,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -16182,7 +16194,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -16200,7 +16212,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -16218,7 +16230,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -16236,7 +16248,7 @@
     </row>
     <row r="38" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -16244,11 +16256,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -16258,7 +16270,7 @@
     </row>
     <row r="39" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -16266,11 +16278,11 @@
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H39" s="11"/>
       <c r="I39" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -16280,7 +16292,7 @@
     </row>
     <row r="40" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -16288,11 +16300,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -16321,7 +16333,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -16391,11 +16403,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -16413,7 +16425,7 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -16433,7 +16445,7 @@
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -16453,11 +16465,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -16475,7 +16487,7 @@
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -16559,7 +16571,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -16577,7 +16589,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -16595,7 +16607,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -16613,7 +16625,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -16631,7 +16643,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -16649,7 +16661,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -16667,7 +16679,7 @@
     </row>
     <row r="18" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -16675,11 +16687,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -16689,7 +16701,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -16707,7 +16719,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -16725,7 +16737,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -16743,7 +16755,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -16761,7 +16773,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -16779,7 +16791,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -16797,7 +16809,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -16815,7 +16827,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -16833,7 +16845,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -16851,7 +16863,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -16869,7 +16881,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -16887,7 +16899,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -16905,7 +16917,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -16923,7 +16935,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -16941,7 +16953,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -16959,7 +16971,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -16977,7 +16989,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -16995,7 +17007,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -17013,7 +17025,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -17031,7 +17043,7 @@
     </row>
     <row r="38" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -17039,7 +17051,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -17051,7 +17063,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -17069,7 +17081,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -17106,7 +17118,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -17176,7 +17188,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
@@ -17332,7 +17344,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -17350,7 +17362,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -17368,7 +17380,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -17386,7 +17398,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -17404,7 +17416,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -17422,7 +17434,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -17440,7 +17452,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -17458,7 +17470,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -17476,7 +17488,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -17494,7 +17506,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -17512,7 +17524,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -17530,7 +17542,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -17548,7 +17560,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -17566,7 +17578,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -17584,7 +17596,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -17602,7 +17614,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -17620,7 +17632,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -17638,7 +17650,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -17656,7 +17668,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -17674,7 +17686,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -17692,7 +17704,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -17710,7 +17722,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -17728,7 +17740,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -17746,7 +17758,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -17764,7 +17776,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -17782,7 +17794,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -17800,7 +17812,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -17818,7 +17830,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -17836,7 +17848,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -17873,7 +17885,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -17943,11 +17955,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -18101,7 +18113,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -18119,7 +18131,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -18137,7 +18149,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -18155,7 +18167,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -18173,7 +18185,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -18191,7 +18203,7 @@
     </row>
     <row r="17" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -18199,7 +18211,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -18211,7 +18223,7 @@
     </row>
     <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -18219,11 +18231,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -18233,7 +18245,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -18251,7 +18263,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -18269,7 +18281,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -18287,7 +18299,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -18305,7 +18317,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -18323,7 +18335,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -18341,7 +18353,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -18359,7 +18371,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -18377,7 +18389,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -18395,7 +18407,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -18413,7 +18425,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -18431,7 +18443,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -18449,7 +18461,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -18467,7 +18479,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -18485,7 +18497,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -18503,7 +18515,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -18521,7 +18533,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -18539,7 +18551,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -18557,7 +18569,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -18575,7 +18587,7 @@
     </row>
     <row r="38" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -18583,11 +18595,11 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -18597,7 +18609,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -18615,7 +18627,7 @@
     </row>
     <row r="40" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -18623,11 +18635,11 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H40" s="11"/>
       <c r="I40" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
@@ -18656,7 +18668,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18880,7 +18892,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -18898,7 +18910,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -18916,7 +18928,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -18934,7 +18946,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -18952,7 +18964,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -18970,7 +18982,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -18988,7 +19000,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -19006,7 +19018,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -19024,7 +19036,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -19042,7 +19054,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -19060,7 +19072,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -19078,7 +19090,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -19096,7 +19108,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -19114,7 +19126,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -19132,7 +19144,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -19150,7 +19162,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -19168,7 +19180,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -19186,7 +19198,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -19204,7 +19216,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -19222,7 +19234,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -19240,7 +19252,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -19258,7 +19270,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -19276,7 +19288,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -19294,7 +19306,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -19312,7 +19324,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -19330,7 +19342,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -19348,7 +19360,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -19366,7 +19378,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -19384,7 +19396,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -19421,7 +19433,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -19645,7 +19657,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -19663,7 +19675,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -19681,7 +19693,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -19699,7 +19711,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -19717,7 +19729,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -19735,7 +19747,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -19753,7 +19765,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -19771,7 +19783,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -19789,7 +19801,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -19807,7 +19819,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -19825,7 +19837,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -19843,7 +19855,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -19861,7 +19873,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -19879,7 +19891,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -19897,7 +19909,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -19915,7 +19927,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -19933,7 +19945,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -19951,7 +19963,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -19969,7 +19981,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -19987,7 +19999,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -20005,7 +20017,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -20023,7 +20035,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -20041,7 +20053,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -20059,7 +20071,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -20077,7 +20089,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -20095,7 +20107,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -20113,7 +20125,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -20131,7 +20143,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -20149,7 +20161,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -20186,7 +20198,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -20256,11 +20268,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -20314,11 +20326,11 @@
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J6" s="11"/>
       <c r="K6" s="11"/>
@@ -20418,7 +20430,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -20436,7 +20448,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="11"/>
       <c r="C13" s="11"/>
@@ -20454,7 +20466,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -20472,7 +20484,7 @@
     </row>
     <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="11"/>
       <c r="C15" s="11"/>
@@ -20480,7 +20492,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -20492,7 +20504,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -20510,7 +20522,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -20528,7 +20540,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -20546,7 +20558,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -20564,7 +20576,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -20582,7 +20594,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -20600,7 +20612,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -20618,7 +20630,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -20636,7 +20648,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -20654,7 +20666,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -20672,7 +20684,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -20690,7 +20702,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -20708,7 +20720,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -20726,7 +20738,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -20744,7 +20756,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -20762,7 +20774,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -20780,7 +20792,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -20798,7 +20810,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -20816,7 +20828,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -20834,7 +20846,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -20852,7 +20864,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -20870,7 +20882,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -20888,7 +20900,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -20906,7 +20918,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -20924,7 +20936,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>

--- a/public/管理口径原因分析默认模版/南京项目部.xlsx
+++ b/public/管理口径原因分析默认模版/南京项目部.xlsx
@@ -9,30 +9,30 @@
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="江苏销售分公司配餐业务" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="江苏非油销售公司劳务输出" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="江苏南京销售分公司劳务输出_合并" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="江苏南京销售分公司劳务输出_222200150520" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="江苏南京销售分公司劳务输出_SH3J25Z017" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="东北销售浙江南京分公司配餐业务" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="江苏南京中石油联安石化办公物业_合并" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="江苏南京中石油联安石化办公物业_222200150531" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="江苏南京中石油联安石化办公物业_SH3626Z003" state="visible" r:id="rId14"/>
-    <sheet sheetId="13" name="江苏镇江销售分公司劳务输出_合并" state="visible" r:id="rId15"/>
-    <sheet sheetId="14" name="江苏镇江销售分公司劳务输出_222200150532" state="visible" r:id="rId16"/>
-    <sheet sheetId="15" name="江苏镇江销售分公司劳务输出_SH3J26Z001" state="visible" r:id="rId17"/>
-    <sheet sheetId="16" name="秣陵路99号综合楼酒店整租项目" state="visible" r:id="rId18"/>
-    <sheet sheetId="17" name="黄鹂新村8栋酒店整租项目" state="visible" r:id="rId19"/>
-    <sheet sheetId="18" name="黄鹂新村、金斯利、南湖住宅其他资产租赁项目" state="visible" r:id="rId20"/>
-    <sheet sheetId="19" name="南京项目部项目销售" state="visible" r:id="rId21"/>
-    <sheet sheetId="20" name="南京酒店能源转售项目" state="visible" r:id="rId22"/>
-    <sheet sheetId="21" name="中国移动南京分公司基站" state="visible" r:id="rId23"/>
-    <sheet sheetId="22" name="中国铁塔南京市分公司基站" state="visible" r:id="rId24"/>
-    <sheet sheetId="23" name="合肥昆仑燃气配餐项目" state="visible" r:id="rId25"/>
-    <sheet sheetId="24" name="天然气安徽分配餐项目" state="visible" r:id="rId26"/>
-    <sheet sheetId="25" name="中石油昆仑合燃压缩气配餐项目" state="visible" r:id="rId27"/>
-    <sheet sheetId="26" name="东北销售南京分计量服务项目" state="visible" r:id="rId28"/>
-    <sheet sheetId="27" name="江苏淮安销售分公司配餐劳务项目" state="visible" r:id="rId29"/>
+    <sheet sheetId="4" name="江苏销售配餐" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="江苏非油劳务" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="南京劳务输出_合并" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="南京劳务输出_222200150520" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="南京劳务输出_SH3J25Z017" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="东北销售南京分配餐" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="三江口物业_合并" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="三江口物业_222200150531" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="三江口物业_SH3626Z003" state="visible" r:id="rId14"/>
+    <sheet sheetId="13" name="镇江劳务输出_合并" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="镇江劳务输出_222200150532" state="visible" r:id="rId16"/>
+    <sheet sheetId="15" name="镇江劳务输出_SH3J26Z001" state="visible" r:id="rId17"/>
+    <sheet sheetId="16" name="秣陵路综合楼整租" state="visible" r:id="rId18"/>
+    <sheet sheetId="17" name="黄鹂新村整租" state="visible" r:id="rId19"/>
+    <sheet sheetId="18" name="其他住宅租赁" state="visible" r:id="rId20"/>
+    <sheet sheetId="19" name="南京项目部销售" state="visible" r:id="rId21"/>
+    <sheet sheetId="20" name="南京能源转售" state="visible" r:id="rId22"/>
+    <sheet sheetId="21" name="移动南京基站" state="visible" r:id="rId23"/>
+    <sheet sheetId="22" name="铁塔南京基站" state="visible" r:id="rId24"/>
+    <sheet sheetId="23" name="合肥配餐" state="visible" r:id="rId25"/>
+    <sheet sheetId="24" name="天然气配餐" state="visible" r:id="rId26"/>
+    <sheet sheetId="25" name="合燃压缩气配餐" state="visible" r:id="rId27"/>
+    <sheet sheetId="26" name="东北南京计量" state="visible" r:id="rId28"/>
+    <sheet sheetId="27" name="淮安劳务输出" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -56,76 +56,76 @@
     <t>合计</t>
   </si>
   <si>
-    <t>江苏销售分公司配餐业务</t>
+    <t>江苏销售配餐</t>
   </si>
   <si>
-    <t>江苏非油销售公司劳务输出</t>
+    <t>江苏非油劳务</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_合并</t>
+    <t>南京劳务输出_合并</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_222200150520</t>
+    <t>南京劳务输出_222200150520</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_SH3J25Z017</t>
+    <t>南京劳务输出_SH3J25Z017</t>
   </si>
   <si>
-    <t>东北销售浙江南京分公司配餐业务</t>
+    <t>东北销售南京分配餐</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_合并</t>
+    <t>三江口物业_合并</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_222200150531</t>
+    <t>三江口物业_222200150531</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_SH3626Z003</t>
+    <t>三江口物业_SH3626Z003</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_合并</t>
+    <t>镇江劳务输出_合并</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_222200150532</t>
+    <t>镇江劳务输出_222200150532</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_SH3J26Z001</t>
+    <t>镇江劳务输出_SH3J26Z001</t>
   </si>
   <si>
-    <t>秣陵路99号综合楼酒店整租项目</t>
+    <t>秣陵路综合楼整租</t>
   </si>
   <si>
-    <t>黄鹂新村8栋酒店整租项目</t>
+    <t>黄鹂新村整租</t>
   </si>
   <si>
-    <t>黄鹂新村、金斯利、南湖住宅其他资产租赁项目</t>
+    <t>其他住宅租赁</t>
   </si>
   <si>
-    <t>南京项目部项目销售</t>
+    <t>南京项目部销售</t>
   </si>
   <si>
-    <t>南京酒店能源转售项目</t>
+    <t>南京能源转售</t>
   </si>
   <si>
-    <t>中国移动南京分公司基站</t>
+    <t>移动南京基站</t>
   </si>
   <si>
-    <t>中国铁塔南京市分公司基站</t>
+    <t>铁塔南京基站</t>
   </si>
   <si>
-    <t>合肥昆仑燃气配餐项目</t>
+    <t>合肥配餐</t>
   </si>
   <si>
-    <t>天然气安徽分配餐项目</t>
+    <t>天然气配餐</t>
   </si>
   <si>
-    <t>中石油昆仑合燃压缩气配餐项目</t>
+    <t>合燃压缩气配餐</t>
   </si>
   <si>
-    <t>东北销售南京分计量服务项目</t>
+    <t>东北南京计量</t>
   </si>
   <si>
-    <t>江苏淮安销售分公司配餐劳务项目</t>
+    <t>淮安劳务输出</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -386,7 +386,7 @@
     <t>主要因所得税汇算清缴25年已预提及新增配餐增加利润</t>
   </si>
   <si>
-    <t>江苏销售分公司配餐业务预算执行分析（2026年08月）</t>
+    <t>江苏销售配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目据实结算，原东北销售南京分部分人员转移此用餐</t>
@@ -410,13 +410,13 @@
     <t>江苏销售去年7月单月有二季度结算，本年季度结算在6月，季度结算时会有实际结算与预估差异。</t>
   </si>
   <si>
-    <t>江苏非油销售公司劳务输出预算执行分析（2026年08月）</t>
+    <t>江苏非油劳务预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目合同2025年1月16日到期，用工2人1月人工已结清，自然终止无补偿金。</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
+    <t>南京劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>同期比较增加原因今年合同额增加。</t>
@@ -428,13 +428,13 @@
     <t>新上系统，去年5月人工没进系统，并新合同，增加一人</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_222200150520预算执行分析（2026年08月）</t>
+    <t>南京劳务输出_222200150520预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏南京销售分公司劳务输出_SH3J25Z017预算执行分析（2026年08月）</t>
+    <t>南京劳务输出_SH3J25Z017预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>东北销售浙江南京分公司配餐业务预算执行分析（2026年08月）</t>
+    <t>东北销售南京分配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新上系统，去年5月收入未进账</t>
@@ -449,7 +449,7 @@
     <t>根据收入比例计提税费</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_合并预算执行分析（2026年08月）</t>
+    <t>三江口物业_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新上系统，去年5月收入同比未入账</t>
@@ -473,13 +473,13 @@
     <t>4人未交社保减少成本利润增加</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_222200150531预算执行分析（2026年08月）</t>
+    <t>三江口物业_222200150531预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏南京中石油联安石化办公物业_SH3626Z003预算执行分析（2026年08月）</t>
+    <t>三江口物业_SH3626Z003预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
+    <t>镇江劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新上系统，去年5月收入未入账</t>
@@ -491,13 +491,13 @@
     <t>人工加班费成本增加利润下降</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_222200150532预算执行分析（2026年08月）</t>
+    <t>镇江劳务输出_222200150532预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏镇江销售分公司劳务输出_SH3J26Z001预算执行分析（2026年08月）</t>
+    <t>镇江劳务输出_SH3J26Z001预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>秣陵路99号综合楼酒店整租项目预算执行分析（2026年08月）</t>
+    <t>秣陵路综合楼整租预算执行分析（2026年08月）</t>
   </si>
   <si>
     <r>
@@ -602,7 +602,7 @@
     <t>主要因素为所得税汇算清缴已在25年预提</t>
   </si>
   <si>
-    <t>黄鹂新村8栋酒店整租项目预算执行分析（2026年08月）</t>
+    <t>黄鹂新村整租预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>减免7月、8月收入</t>
@@ -611,7 +611,7 @@
     <t>减免7月、8月收入相关税费减少</t>
   </si>
   <si>
-    <t>黄鹂新村、金斯利、南湖住宅其他资产租赁项目预算执行分析（2026年08月）</t>
+    <t>其他住宅租赁预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t xml:space="preserve">同比租金协议下降 </t>
@@ -623,19 +623,19 @@
     <t>同比租金协议下降，影响利润</t>
   </si>
   <si>
-    <t>南京项目部项目销售预算执行分析（2026年08月）</t>
+    <t>南京项目部销售预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>粽子销售客源流失</t>
   </si>
   <si>
-    <t>南京酒店能源转售项目预算执行分析（2026年08月）</t>
+    <t>南京能源转售预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>非盈利项目</t>
   </si>
   <si>
-    <t>中国移动南京分公司基站预算执行分析（2026年08月）</t>
+    <t>移动南京基站预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>移动租金递增</t>
@@ -648,7 +648,7 @@
 </t>
   </si>
   <si>
-    <t>中国铁塔南京市分公司基站预算执行分析（2026年08月）</t>
+    <t>铁塔南京基站预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>同比租金下降</t>
@@ -664,7 +664,7 @@
 </t>
   </si>
   <si>
-    <t>合肥昆仑燃气配餐项目预算执行分析（2026年08月）</t>
+    <t>合肥配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>食材据实结算</t>
@@ -676,7 +676,7 @@
     <t>新增零星用餐业务收入新增利润</t>
   </si>
   <si>
-    <t>天然气安徽分配餐项目预算执行分析（2026年08月）</t>
+    <t>天然气配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新能源部门调到其他地方</t>
@@ -688,7 +688,7 @@
     <t>聘用3名退休人员，控人工成本</t>
   </si>
   <si>
-    <t>中石油昆仑合燃压缩气配餐项目预算执行分析（2026年08月）</t>
+    <t>合燃压缩气配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>去年新增项目</t>
@@ -697,7 +697,7 @@
     <t>收入根据食材有所变动</t>
   </si>
   <si>
-    <t>东北销售南京分计量服务项目预算执行分析（2026年08月）</t>
+    <t>东北南京计量预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>原合同预算按3月终止，因续签1年延长了存续期，收入偏差较大</t>
@@ -712,7 +712,7 @@
     <t>原合同预算按3月终止，净利润指标2.7万元，因续签1年延长了存续期，利润偏差较大</t>
   </si>
   <si>
-    <t>江苏淮安销售分公司配餐劳务项目预算执行分析（2026年08月）</t>
+    <t>淮安劳务输出预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新增项目</t>
@@ -9022,7 +9022,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f>HYPERLINK("#'江苏销售分公司配餐业务'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'江苏销售配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>HYPERLINK("#'江苏非油销售公司劳务输出'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'江苏非油劳务'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'江苏南京销售分公司劳务输出_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南京劳务输出_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'江苏南京销售分公司劳务输出_222200150520'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南京劳务输出_222200150520'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'江苏南京销售分公司劳务输出_SH3J25Z017'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南京劳务输出_SH3J25Z017'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>HYPERLINK("#'东北销售浙江南京分公司配餐业务'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'东北销售南京分配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>HYPERLINK("#'江苏南京中石油联安石化办公物业_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'三江口物业_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>HYPERLINK("#'江苏南京中石油联安石化办公物业_222200150531'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'三江口物业_222200150531'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>HYPERLINK("#'江苏南京中石油联安石化办公物业_SH3626Z003'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'三江口物业_SH3626Z003'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>HYPERLINK("#'江苏镇江销售分公司劳务输出_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'镇江劳务输出_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f>HYPERLINK("#'江苏镇江销售分公司劳务输出_222200150532'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'镇江劳务输出_222200150532'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>HYPERLINK("#'江苏镇江销售分公司劳务输出_SH3J26Z001'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'镇江劳务输出_SH3J26Z001'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="5" t="str">
-        <f>HYPERLINK("#'秣陵路99号综合楼酒店整租项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'秣陵路综合楼整租'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f>HYPERLINK("#'黄鹂新村8栋酒店整租项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'黄鹂新村整租'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="5" t="str">
-        <f>HYPERLINK("#'黄鹂新村、金斯利、南湖住宅其他资产租赁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'其他住宅租赁'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="5" t="str">
-        <f>HYPERLINK("#'南京项目部项目销售'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南京项目部销售'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="5" t="str">
-        <f>HYPERLINK("#'南京酒店能源转售项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南京能源转售'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="5" t="str">
-        <f>HYPERLINK("#'中国移动南京分公司基站'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'移动南京基站'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="5" t="str">
-        <f>HYPERLINK("#'中国铁塔南京市分公司基站'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'铁塔南京基站'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="5" t="str">
-        <f>HYPERLINK("#'合肥昆仑燃气配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'合肥配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9222,7 +9222,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="5" t="str">
-        <f>HYPERLINK("#'天然气安徽分配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'天然气配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="5" t="str">
-        <f>HYPERLINK("#'中石油昆仑合燃压缩气配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'合燃压缩气配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="5" t="str">
-        <f>HYPERLINK("#'东北销售南京分计量服务项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'东北南京计量'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="5" t="str">
-        <f>HYPERLINK("#'江苏淮安销售分公司配餐劳务项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'淮安劳务输出'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
